--- a/Design-Files/ArmBand-Sensor-Board-v2.0/BOM/JLCPCB_BOM.xlsx
+++ b/Design-Files/ArmBand-Sensor-Board-v2.0/BOM/JLCPCB_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ManarHarake-sEMGDevice\Design-Files\ArmBand-Sensor-Board-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ManarHarake-sEMGDevice\Design-Files\ArmBand-Sensor-Board-v2.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>Comment</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>C2923365</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>C71035</t>
@@ -690,7 +693,9 @@
       <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -745,7 +750,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
